--- a/XBRL-template-MFRS/Group/02-SOFP-OrderOfLiquidity.xlsx
+++ b/XBRL-template-MFRS/Group/02-SOFP-OrderOfLiquidity.xlsx
@@ -948,10 +948,22 @@
           <t>Assets other than assets held for sale</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="22" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="22" t="n"/>
+      <c r="B25" s="22">
+        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B24</f>
+        <v/>
+      </c>
+      <c r="C25" s="22">
+        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="22">
+        <f>1*D7+1*D8+1*D9+1*D10+1*D11+1*D12+1*D13+1*D14+1*D15+1*D16+1*D17+1*D18+1*D19+1*D20+1*D21+1*D22+1*D23+1*D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="22">
+        <f>1*E7+1*E8+1*E9+1*E10+1*E11+1*E12+1*E13+1*E14+1*E15+1*E16+1*E17+1*E18+1*E19+1*E20+1*E21+1*E22+1*E23+1*E24</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="12">
       <c r="A26" s="19" t="inlineStr">
@@ -959,22 +971,10 @@
           <t>Total non-current assets or disposal groups classified as held for sale or as held for distribution to owners</t>
         </is>
       </c>
-      <c r="B26" s="20">
-        <f>1*B24+1*B25</f>
-        <v/>
-      </c>
-      <c r="C26" s="20">
-        <f>1*C24+1*C25</f>
-        <v/>
-      </c>
-      <c r="D26" s="20">
-        <f>1*D24+1*D25</f>
-        <v/>
-      </c>
-      <c r="E26" s="20">
-        <f>1*E24+1*E25</f>
-        <v/>
-      </c>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="12">
       <c r="A27" s="19" t="inlineStr">
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="B27" s="23">
-        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B26</f>
+        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B24+1*B26</f>
         <v/>
       </c>
       <c r="C27" s="23">
-        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C26</f>
+        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C24+1*C26</f>
         <v/>
       </c>
       <c r="D27" s="23">
-        <f>1*D7+1*D8+1*D9+1*D10+1*D11+1*D12+1*D13+1*D14+1*D15+1*D16+1*D17+1*D18+1*D19+1*D20+1*D21+1*D22+1*D23+1*D26</f>
+        <f>1*D7+1*D8+1*D9+1*D10+1*D11+1*D12+1*D13+1*D14+1*D15+1*D16+1*D17+1*D18+1*D19+1*D20+1*D21+1*D22+1*D23+1*D24+1*D26</f>
         <v/>
       </c>
       <c r="E27" s="23">
-        <f>1*E7+1*E8+1*E9+1*E10+1*E11+1*E12+1*E13+1*E14+1*E15+1*E16+1*E17+1*E18+1*E19+1*E20+1*E21+1*E22+1*E23+1*E26</f>
+        <f>1*E7+1*E8+1*E9+1*E10+1*E11+1*E12+1*E13+1*E14+1*E15+1*E16+1*E17+1*E18+1*E19+1*E20+1*E21+1*E22+1*E23+1*E24+1*E26</f>
         <v/>
       </c>
     </row>
@@ -1153,19 +1153,19 @@
         </is>
       </c>
       <c r="B37" s="23">
-        <f>1*B34+1*B35+1*B36</f>
+        <f>1*B30+1*B31+-1*B32+1*B33+1*B35+1*B36</f>
         <v/>
       </c>
       <c r="C37" s="23">
-        <f>1*C34+1*C35+1*C36</f>
+        <f>1*C30+1*C31+-1*C32+1*C33+1*C35+1*C36</f>
         <v/>
       </c>
       <c r="D37" s="23">
-        <f>1*D34+1*D35+1*D36</f>
+        <f>1*D30+1*D31+-1*D32+1*D33+1*D35+1*D36</f>
         <v/>
       </c>
       <c r="E37" s="23">
-        <f>1*E34+1*E35+1*E36</f>
+        <f>1*E30+1*E31+-1*E32+1*E33+1*E35+1*E36</f>
         <v/>
       </c>
     </row>
@@ -1311,22 +1311,10 @@
           <t>Total contract liabilities</t>
         </is>
       </c>
-      <c r="B46" s="20">
-        <f>1*B45</f>
-        <v/>
-      </c>
-      <c r="C46" s="20">
-        <f>1*C45</f>
-        <v/>
-      </c>
-      <c r="D46" s="20">
-        <f>1*D45</f>
-        <v/>
-      </c>
-      <c r="E46" s="20">
-        <f>1*E45</f>
-        <v/>
-      </c>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1" s="12">
       <c r="A47" s="21" t="inlineStr">
@@ -1379,10 +1367,22 @@
           <t>Liabilities other than liabilities held for sale</t>
         </is>
       </c>
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="22" t="n"/>
+      <c r="B50" s="22">
+        <f>1*B39+1*B40+1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49</f>
+        <v/>
+      </c>
+      <c r="C50" s="22">
+        <f>1*C39+1*C40+1*C41+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49</f>
+        <v/>
+      </c>
+      <c r="D50" s="22">
+        <f>1*D39+1*D40+1*D41+1*D42+1*D43+1*D44+1*D45+1*D46+1*D47+1*D48+1*D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="22">
+        <f>1*E39+1*E40+1*E41+1*E42+1*E43+1*E44+1*E45+1*E46+1*E47+1*E48+1*E49</f>
+        <v/>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="12">
       <c r="A51" s="21" t="inlineStr">
@@ -1402,19 +1402,19 @@
         </is>
       </c>
       <c r="B52" s="20">
-        <f>1*B39+1*B40+1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B50+1*B51</f>
+        <f>1*B39+1*B40+1*B41+1*B42+1*B43+1*B44+1*B45+1*B46+1*B47+1*B48+1*B49+1*B51</f>
         <v/>
       </c>
       <c r="C52" s="20">
-        <f>1*C39+1*C40+1*C41+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C50+1*C51</f>
+        <f>1*C39+1*C40+1*C41+1*C42+1*C43+1*C44+1*C45+1*C46+1*C47+1*C48+1*C49+1*C51</f>
         <v/>
       </c>
       <c r="D52" s="20">
-        <f>1*D39+1*D40+1*D41+1*D42+1*D43+1*D44+1*D45+1*D46+1*D47+1*D48+1*D49+1*D50+1*D51</f>
+        <f>1*D39+1*D40+1*D41+1*D42+1*D43+1*D44+1*D45+1*D46+1*D47+1*D48+1*D49+1*D51</f>
         <v/>
       </c>
       <c r="E52" s="20">
-        <f>1*E39+1*E40+1*E41+1*E42+1*E43+1*E44+1*E45+1*E46+1*E47+1*E48+1*E49+1*E50+1*E51</f>
+        <f>1*E39+1*E40+1*E41+1*E42+1*E43+1*E44+1*E45+1*E46+1*E47+1*E48+1*E49+1*E51</f>
         <v/>
       </c>
     </row>
@@ -1713,19 +1713,19 @@
         </is>
       </c>
       <c r="B19" s="23">
-        <f>1*B14+1*B15+1*B16+1*B17+1*B18</f>
+        <f>1*B12+1*B18</f>
         <v/>
       </c>
       <c r="C19" s="23">
-        <f>1*C14+1*C15+1*C16+1*C17+1*C18</f>
+        <f>1*C12+1*C18</f>
         <v/>
       </c>
       <c r="D19" s="23">
-        <f>1*D14+1*D15+1*D16+1*D17+1*D18</f>
+        <f>1*D12+1*D18</f>
         <v/>
       </c>
       <c r="E19" s="23">
-        <f>1*E14+1*E15+1*E16+1*E17+1*E18</f>
+        <f>1*E12+1*E18</f>
         <v/>
       </c>
     </row>
@@ -2057,10 +2057,22 @@
           <t>Investment property under construction or development</t>
         </is>
       </c>
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="22" t="n"/>
+      <c r="B46" s="22">
+        <f>1*B45</f>
+        <v/>
+      </c>
+      <c r="C46" s="22">
+        <f>1*C45</f>
+        <v/>
+      </c>
+      <c r="D46" s="22">
+        <f>1*D45</f>
+        <v/>
+      </c>
+      <c r="E46" s="22">
+        <f>1*E45</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="12">
       <c r="A47" s="21" t="inlineStr">
@@ -2080,19 +2092,19 @@
         </is>
       </c>
       <c r="B48" s="23">
-        <f>1*B41+1*B42+1*B43+1*B45+1*B46+1*B47</f>
+        <f>1*B43+1*B46+1*B47</f>
         <v/>
       </c>
       <c r="C48" s="23">
-        <f>1*C41+1*C42+1*C43+1*C45+1*C46+1*C47</f>
+        <f>1*C43+1*C46+1*C47</f>
         <v/>
       </c>
       <c r="D48" s="23">
-        <f>1*D41+1*D42+1*D43+1*D45+1*D46+1*D47</f>
+        <f>1*D43+1*D46+1*D47</f>
         <v/>
       </c>
       <c r="E48" s="23">
-        <f>1*E41+1*E42+1*E43+1*E45+1*E46+1*E47</f>
+        <f>1*E43+1*E46+1*E47</f>
         <v/>
       </c>
     </row>
@@ -2547,19 +2559,19 @@
         </is>
       </c>
       <c r="B85" s="24">
-        <f>1*B79+1*B80+1*B81+1*B83+1*B84</f>
+        <f>1*B78+1*B79+1*B80+1*B81+1*B82+1*B83+1*B84</f>
         <v/>
       </c>
       <c r="C85" s="24">
-        <f>1*C79+1*C80+1*C81+1*C83+1*C84</f>
+        <f>1*C78+1*C79+1*C80+1*C81+1*C82+1*C83+1*C84</f>
         <v/>
       </c>
       <c r="D85" s="24">
-        <f>1*D79+1*D80+1*D81+1*D83+1*D84</f>
+        <f>1*D78+1*D79+1*D80+1*D81+1*D82+1*D83+1*D84</f>
         <v/>
       </c>
       <c r="E85" s="24">
-        <f>1*E79+1*E80+1*E81+1*E83+1*E84</f>
+        <f>1*E78+1*E79+1*E80+1*E81+1*E82+1*E83+1*E84</f>
         <v/>
       </c>
     </row>
@@ -2658,19 +2670,19 @@
         </is>
       </c>
       <c r="B94" s="24">
-        <f>1*B87+1*B88+1*B89+1*B90+1*B92+1*B93</f>
+        <f>1*B87+1*B88+1*B89+1*B90+1*B91+1*B92+1*B93</f>
         <v/>
       </c>
       <c r="C94" s="24">
-        <f>1*C87+1*C88+1*C89+1*C90+1*C92+1*C93</f>
+        <f>1*C87+1*C88+1*C89+1*C90+1*C91+1*C92+1*C93</f>
         <v/>
       </c>
       <c r="D94" s="24">
-        <f>1*D87+1*D88+1*D89+1*D90+1*D92+1*D93</f>
+        <f>1*D87+1*D88+1*D89+1*D90+1*D91+1*D92+1*D93</f>
         <v/>
       </c>
       <c r="E94" s="24">
-        <f>1*E87+1*E88+1*E89+1*E90+1*E92+1*E93</f>
+        <f>1*E87+1*E88+1*E89+1*E90+1*E91+1*E92+1*E93</f>
         <v/>
       </c>
     </row>
@@ -3093,19 +3105,19 @@
         </is>
       </c>
       <c r="B127" s="23">
-        <f>1*B124</f>
+        <f>1*B107+1*B126</f>
         <v/>
       </c>
       <c r="C127" s="23">
-        <f>1*C124</f>
+        <f>1*C107+1*C126</f>
         <v/>
       </c>
       <c r="D127" s="23">
-        <f>1*D124</f>
+        <f>1*D107+1*D126</f>
         <v/>
       </c>
       <c r="E127" s="23">
-        <f>1*E124</f>
+        <f>1*E107+1*E126</f>
         <v/>
       </c>
     </row>
@@ -3772,10 +3784,22 @@
           <t>Non-distributable other reserves</t>
         </is>
       </c>
-      <c r="B179" s="24" t="n"/>
-      <c r="C179" s="24" t="n"/>
-      <c r="D179" s="24" t="n"/>
-      <c r="E179" s="24" t="n"/>
+      <c r="B179" s="24">
+        <f>1*B171+1*B172+1*B173+1*B174+1*B175+1*B176+1*B177+1*B178</f>
+        <v/>
+      </c>
+      <c r="C179" s="24">
+        <f>1*C171+1*C172+1*C173+1*C174+1*C175+1*C176+1*C177+1*C178</f>
+        <v/>
+      </c>
+      <c r="D179" s="24">
+        <f>1*D171+1*D172+1*D173+1*D174+1*D175+1*D176+1*D177+1*D178</f>
+        <v/>
+      </c>
+      <c r="E179" s="24">
+        <f>1*E171+1*E172+1*E173+1*E174+1*E175+1*E176+1*E177+1*E178</f>
+        <v/>
+      </c>
     </row>
     <row r="180" ht="18" customHeight="1" s="12">
       <c r="A180" s="17" t="inlineStr">
@@ -3849,10 +3873,22 @@
           <t>Distributable reserves</t>
         </is>
       </c>
-      <c r="B186" s="22" t="n"/>
-      <c r="C186" s="22" t="n"/>
-      <c r="D186" s="22" t="n"/>
-      <c r="E186" s="22" t="n"/>
+      <c r="B186" s="22">
+        <f>1*B181+1*B182+1*B183+1*B184+1*B185</f>
+        <v/>
+      </c>
+      <c r="C186" s="22">
+        <f>1*C181+1*C182+1*C183+1*C184+1*C185</f>
+        <v/>
+      </c>
+      <c r="D186" s="22">
+        <f>1*D181+1*D182+1*D183+1*D184+1*D185</f>
+        <v/>
+      </c>
+      <c r="E186" s="22">
+        <f>1*E181+1*E182+1*E183+1*E184+1*E185</f>
+        <v/>
+      </c>
     </row>
     <row r="187" ht="18" customHeight="1" s="12">
       <c r="A187" s="19" t="inlineStr">
@@ -3861,19 +3897,19 @@
         </is>
       </c>
       <c r="B187" s="23">
-        <f>1*B171+1*B172+1*B173+1*B174+1*B175+1*B176+1*B177+1*B178+1*B179+1*B181+1*B182+1*B183+1*B184+1*B185+1*B186</f>
+        <f>1*B179+1*B186</f>
         <v/>
       </c>
       <c r="C187" s="23">
-        <f>1*C171+1*C172+1*C173+1*C174+1*C175+1*C176+1*C177+1*C178+1*C179+1*C181+1*C182+1*C183+1*C184+1*C185+1*C186</f>
+        <f>1*C179+1*C186</f>
         <v/>
       </c>
       <c r="D187" s="23">
-        <f>1*D171+1*D172+1*D173+1*D174+1*D175+1*D176+1*D177+1*D178+1*D179+1*D181+1*D182+1*D183+1*D184+1*D185+1*D186</f>
+        <f>1*D179+1*D186</f>
         <v/>
       </c>
       <c r="E187" s="23">
-        <f>1*E171+1*E172+1*E173+1*E174+1*E175+1*E176+1*E177+1*E178+1*E179+1*E181+1*E182+1*E183+1*E184+1*E185+1*E186</f>
+        <f>1*E179+1*E186</f>
         <v/>
       </c>
     </row>
@@ -4650,19 +4686,19 @@
         </is>
       </c>
       <c r="B250" s="24">
-        <f>1*B244+1*B245+1*B246+1*B247+1*B248+1*B249</f>
+        <f>1*B243+1*B244+1*B245+1*B246+1*B247+1*B248+1*B249</f>
         <v/>
       </c>
       <c r="C250" s="24">
-        <f>1*C244+1*C245+1*C246+1*C247+1*C248+1*C249</f>
+        <f>1*C243+1*C244+1*C245+1*C246+1*C247+1*C248+1*C249</f>
         <v/>
       </c>
       <c r="D250" s="24">
-        <f>1*D244+1*D245+1*D246+1*D247+1*D248+1*D249</f>
+        <f>1*D243+1*D244+1*D245+1*D246+1*D247+1*D248+1*D249</f>
         <v/>
       </c>
       <c r="E250" s="24">
-        <f>1*E244+1*E245+1*E246+1*E247+1*E248+1*E249</f>
+        <f>1*E243+1*E244+1*E245+1*E246+1*E247+1*E248+1*E249</f>
         <v/>
       </c>
     </row>
